--- a/results/naturverbundenheit/observables/nature-dataset-distance-normalized-matrix-jensenshannon-auto.xlsx
+++ b/results/naturverbundenheit/observables/nature-dataset-distance-normalized-matrix-jensenshannon-auto.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ43"/>
+  <dimension ref="A1:AJ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,205 +441,170 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>France</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>India</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>United States of America</t>
         </is>
@@ -655,5579 +620,3913 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0006740641217920537</v>
+        <v>0.0005856565594126641</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004114715094424606</v>
+        <v>0.0005008814591192399</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000281102069428598</v>
+        <v>0.0007916846031915033</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000500170164815914</v>
+        <v>0.001004966969971907</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0006134490865624929</v>
+        <v>0.0009235470317730378</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007393069007340028</v>
+        <v>0.001100041504102932</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0005981195058979399</v>
+        <v>0.001253088501110642</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005655838624190898</v>
+        <v>0.0009675375720748951</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0006335251220954679</v>
+        <v>0.0009041756817274398</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006685364665462279</v>
+        <v>0.0009607586959189257</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004405637442133486</v>
+        <v>0.0007164265981208997</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004779495766345493</v>
+        <v>0.0009459675945561783</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000480605610652216</v>
+        <v>0.0009582409772063966</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0004405813052204726</v>
+        <v>0.0009488099202462937</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0004113330945082985</v>
+        <v>0.001129436336123301</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000565230667631836</v>
+        <v>0.001320267482587458</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0005839289458934497</v>
+        <v>0.001060782537431346</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0005739378765271104</v>
+        <v>0.001353282205319402</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0007251039804901657</v>
+        <v>0.001269677294427742</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001126660024246718</v>
+        <v>0.001127254917991796</v>
       </c>
       <c r="W2" t="n">
-        <v>0.000734388213855064</v>
+        <v>0.00085158425319275</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0006342108497116561</v>
+        <v>0.000614790489828897</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0009019549561920089</v>
+        <v>0.001158886898265506</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0007393416189674431</v>
+        <v>0.001308226828174105</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.000697008349240889</v>
+        <v>0.0008818842859069337</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0004580086659977591</v>
+        <v>0.0009084662551175268</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0002718195129964248</v>
+        <v>0.0005227069412464189</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0005706434410095498</v>
+        <v>0.001016581151108363</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.00063673469988384</v>
+        <v>0.0008552209741915739</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0004839864888133459</v>
+        <v>0.0004394012415861558</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0005290269552407787</v>
+        <v>0.001282131115058952</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0003645856527169618</v>
+        <v>0.0009511910653918536</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0003699283209478568</v>
+        <v>0.0007020564609489156</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0004821103167212461</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.0002697786490594912</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.001317741669889308</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.0008459267421384435</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.0006169735732953483</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.0007222553245433978</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.0004386169712677647</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.0003704476928184742</v>
+        <v>0.0005768535541722726</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006740641217920537</v>
+        <v>0.0005856565594126641</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006431228011161776</v>
+        <v>0.0005945742076993232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00049137270425171</v>
+        <v>0.0008702272273819737</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004379591920638983</v>
+        <v>0.0007734199985464344</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000425616946308428</v>
+        <v>0.0005466325975272051</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008255978899729591</v>
+        <v>0.0008272146831472227</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005483356225501342</v>
+        <v>0.0008548684467236245</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006176551995779067</v>
+        <v>0.0007644850847827463</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004453331002304017</v>
+        <v>0.001021591652926877</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006543043808557071</v>
+        <v>0.0008959486471696157</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0005017517157461259</v>
+        <v>0.0007251886922089658</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0005107235582205779</v>
+        <v>0.001097266362573354</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003378908904315715</v>
+        <v>0.0008228231178222704</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000351766459577166</v>
+        <v>0.0006660478140725422</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0004913508447900556</v>
+        <v>0.001130755305052761</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004530497930058533</v>
+        <v>0.001177183122650688</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005382599388982408</v>
+        <v>0.0009653077411581449</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0005515231002359244</v>
+        <v>0.001037715403188717</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003227188235878585</v>
+        <v>0.001165827692216639</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001065647743215086</v>
+        <v>0.0009002667019520666</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003128964621205048</v>
+        <v>0.0009119101296241693</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0002967896095166707</v>
+        <v>0.0006042601173090152</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000940578647230899</v>
+        <v>0.00126721564878036</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0005031510427692111</v>
+        <v>0.001298516794023601</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0004264106220034558</v>
+        <v>0.0008935761888598859</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0004968318191751726</v>
+        <v>0.000942378112062103</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0005268580059777571</v>
+        <v>0.0006517486766031003</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0005745902505723199</v>
+        <v>0.00103306524695421</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0005817185841383895</v>
+        <v>0.0007515629875129992</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0003660048328737563</v>
+        <v>0.0007243966133843795</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0004856311995679755</v>
+        <v>0.001314225466589096</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0005746881975746118</v>
+        <v>0.0009475910758355988</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0004283309341776023</v>
+        <v>0.0008452465396217436</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.000437567653459304</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.0005679874991989087</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0.001174321718765846</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.0006634900459314878</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.0006182091938677395</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.0005231151869138896</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.0003969471304691086</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.0005179754234304361</v>
+        <v>0.0008147277517888433</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0004114715094424606</v>
+        <v>0.0005008814591192399</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006431228011161776</v>
+        <v>0.0005945742076993232</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004343584419062528</v>
+        <v>0.0004594555126925258</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006043070561240095</v>
+        <v>0.0007761867364682193</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004863288925046214</v>
+        <v>0.0007735906322346575</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000640117282001306</v>
+        <v>0.0009010647078769876</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003393564597925803</v>
+        <v>0.001111861626152161</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000686189974055562</v>
+        <v>0.0006683875157843823</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005060960148814097</v>
+        <v>0.0007183668832259168</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004352941064034891</v>
+        <v>0.000696491221404799</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0004787095603551546</v>
+        <v>0.0004442858669121244</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0006289511202645262</v>
+        <v>0.0008239194027629364</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0004662107924246352</v>
+        <v>0.0007010370037059213</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0004663721258220573</v>
+        <v>0.0008186550815920069</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005573858045588926</v>
+        <v>0.000852290862430361</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004723102215005988</v>
+        <v>0.0009860858573805518</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004520495433414003</v>
+        <v>0.000789996637514659</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0006786825681856127</v>
+        <v>0.001336668618547091</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007701730805420575</v>
+        <v>0.001033872423080682</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0009301244367438554</v>
+        <v>0.0009374861831184352</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0006881429497859296</v>
+        <v>0.0006561334132534017</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005462222857390461</v>
+        <v>0.0004863532518594072</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0006754061655669845</v>
+        <v>0.0009817676313937827</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0006931667545555864</v>
+        <v>0.001069114891990158</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0005706857753433822</v>
+        <v>0.000527098809484083</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0005804598443186148</v>
+        <v>0.0006643854548429914</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0004153484737815141</v>
+        <v>0.0006007749978774581</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0007487259398508012</v>
+        <v>0.0007583656241239655</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0007141320809277437</v>
+        <v>0.0006456427175463645</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0005413245969816206</v>
+        <v>0.0004793378836829273</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0006627880690012334</v>
+        <v>0.001191901080144487</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0004327282287032158</v>
+        <v>0.0008080353512692425</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0005359986213533891</v>
+        <v>0.0003892545268076657</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0004307297634753671</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.0004831982834021954</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0.001404358755389437</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.0008130752717807557</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.0007916012243755582</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.0006825030912465269</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0.000579883434644972</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.0005488723217234611</v>
+        <v>0.0003813758961087732</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000281102069428598</v>
+        <v>0.0007916846031915033</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00049137270425171</v>
+        <v>0.0008702272273819737</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004343584419062528</v>
+        <v>0.0004594555126925258</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003484906317323433</v>
+        <v>0.000699065031353835</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004842300203960639</v>
+        <v>0.0009428154342353859</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0007574210211458047</v>
+        <v>0.0008004712873603038</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0005154430113978832</v>
+        <v>0.001119772856909597</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0005328518070610137</v>
+        <v>0.0006226857540029346</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00056364146230816</v>
+        <v>0.0004143008832643204</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006497816490031337</v>
+        <v>0.000636147117733601</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003107020621736757</v>
+        <v>0.0006992421616504738</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0004215532370601625</v>
+        <v>0.0006530788503909997</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000321387619036637</v>
+        <v>0.00074772921553591</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000232405269837704</v>
+        <v>0.0007635220383634159</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003792270433418355</v>
+        <v>0.0006858284599595559</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0004939252818476571</v>
+        <v>0.0007927086117564957</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0005714601032018018</v>
+        <v>0.0006540611711085323</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0005250204991308747</v>
+        <v>0.001356402818667449</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0005500828560460604</v>
+        <v>0.0007020735230559538</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001140738540474155</v>
+        <v>0.00083131793327742</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0005731914097575591</v>
+        <v>0.0003430664060436905</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0005288076292149178</v>
+        <v>0.0005082118002048126</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0009206542484666157</v>
+        <v>0.0006637867445613288</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0006507739989616225</v>
+        <v>0.0008314665453449499</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0006144990542463208</v>
+        <v>0.0005552551541011322</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0004420264364507378</v>
+        <v>0.0004222623476966967</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0002610036491011894</v>
+        <v>0.0006864462247417092</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0005270550996034893</v>
+        <v>0.0005865657937358622</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0005620492960748789</v>
+        <v>0.0004956959275509188</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.000276708259330582</v>
+        <v>0.000745347913321641</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0004294285847438106</v>
+        <v>0.000879391567803137</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0004543224409601875</v>
+        <v>0.0005552600653124237</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0002942329527747658</v>
+        <v>0.0005518713782784635</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.000396054780798813</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.0002313421278839572</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0.0013119968323427</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.0008409718419795574</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.0005349396953257963</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.0006629158738114783</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0.0002483517573271248</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.0002891177906162364</v>
+        <v>0.0002971606073022798</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000500170164815914</v>
+        <v>0.001004966969971907</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004379591920638983</v>
+        <v>0.0007734199985464344</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0006043070561240095</v>
+        <v>0.0007761867364682193</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003484906317323433</v>
+        <v>0.000699065031353835</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000417426159291</v>
+        <v>0.0008091160454277828</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000752243593060824</v>
+        <v>0.0003556635127440979</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0006446573411350306</v>
+        <v>0.0009230397684784733</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0005408439501383759</v>
+        <v>0.0004084122484917781</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0004892009183266998</v>
+        <v>0.000706540133574218</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0007524612069781442</v>
+        <v>0.0005608568754989707</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0004014861200852862</v>
+        <v>0.0008165403075860928</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002330699275102463</v>
+        <v>0.0009234240083482138</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002819268612039545</v>
+        <v>0.0007668528724721626</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0003804020120800849</v>
+        <v>0.0004418224608108516</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0002317659509750783</v>
+        <v>0.0008712683043069192</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0004794574555122073</v>
+        <v>0.000676279148038398</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0006097709480915672</v>
+        <v>0.0005394600106560362</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0003961888050642167</v>
+        <v>0.001128016612228058</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0005175556892136132</v>
+        <v>0.0006146563129275769</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001119241076217913</v>
+        <v>0.0004980749039133301</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0004722776063476197</v>
+        <v>0.0006213449526627652</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0004032311594832829</v>
+        <v>0.0005063556759874301</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0009125015568296976</v>
+        <v>0.0008993779121150222</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0004485820512320572</v>
+        <v>0.0009845883985982859</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0005037535308594439</v>
+        <v>0.0007154987847545782</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.000333498746066494</v>
+        <v>0.0006050977170366761</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0003829914220709112</v>
+        <v>0.0007873117139946992</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0003065449352845838</v>
+        <v>0.0008466186172826985</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0003906419061804379</v>
+        <v>0.0004643627572829166</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0003450263562126967</v>
+        <v>0.001077862754427846</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0003320290420748173</v>
+        <v>0.0008778135680489995</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0004960767306720012</v>
+        <v>0.0005377055563496869</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0002445126920544164</v>
+        <v>0.0009285070802690865</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.000390534465069385</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.0004448404260821462</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0.001154056158072084</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.0006501954951292626</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.0003693232329259661</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0.0004733742100680559</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0.0003857092896448988</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0.0002320044116464537</v>
+        <v>0.0008440324707272598</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0006134490865624929</v>
+        <v>0.0009235470317730378</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000425616946308428</v>
+        <v>0.0005466325975272051</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0004863288925046214</v>
+        <v>0.0007735906322346575</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0004842300203960639</v>
+        <v>0.0009428154342353859</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000417426159291</v>
+        <v>0.0008091160454277828</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0006779996576899008</v>
+        <v>0.0007770748996268794</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000404398012055835</v>
+        <v>0.0005454023325754224</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0005835391607539858</v>
+        <v>0.0007475274411736167</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001904159685607467</v>
+        <v>0.001111452530874603</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004639010964846237</v>
+        <v>0.0007881580054687012</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0003481818123864901</v>
+        <v>0.0008154435893774109</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0004479445907162552</v>
+        <v>0.001192601733130086</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002601795587123893</v>
+        <v>0.0008405120830800404</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0004698945443488867</v>
+        <v>0.000690041325737788</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0004642458137531928</v>
+        <v>0.001132767161585928</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0003855395128337185</v>
+        <v>0.001077209297632051</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003510383297166774</v>
+        <v>0.0009106047193295413</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0005483133721319726</v>
+        <v>0.001227693073203228</v>
       </c>
       <c r="U7" t="n">
-        <v>0.000588681216164441</v>
+        <v>0.001165519423109031</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008212289531392531</v>
+        <v>0.0008890931404579569</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000353845922369856</v>
+        <v>0.001009971971652721</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0003083164064991587</v>
+        <v>0.0007642372380449213</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0006738441109099467</v>
+        <v>0.001342615308287884</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0002988397306103557</v>
+        <v>0.001268025510384339</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00026637288276816</v>
+        <v>0.0008689470933039331</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004269641611632932</v>
+        <v>0.001097017867519127</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0004096692905454117</v>
+        <v>0.0009621210540979429</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0005681570233592195</v>
+        <v>0.001026984392926785</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0004762503474087923</v>
+        <v>0.0008143500127514107</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0004548591446935832</v>
+        <v>0.0008760129335835358</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0004629808704215372</v>
+        <v>0.001418294500181545</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0005447747687508385</v>
+        <v>0.0009741321181820562</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0004651184046963831</v>
+        <v>0.0009604846523259716</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0002350653712598441</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.0006284985404507103</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0.001297855339353161</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.0005709460674588921</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.0006764319263355303</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.0003875668463317446</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0.0005656445559578215</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.0004814930842745714</v>
+        <v>0.0009703002105510036</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0007393069007340028</v>
+        <v>0.001100041504102932</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0008255978899729591</v>
+        <v>0.0008272146831472227</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000640117282001306</v>
+        <v>0.0009010647078769876</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0007574210211458047</v>
+        <v>0.0008004712873603038</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000752243593060824</v>
+        <v>0.0003556635127440979</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0006779996576899008</v>
+        <v>0.0007770748996268794</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008086919310190328</v>
+        <v>0.000744577828985782</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009925373762933148</v>
+        <v>0.0005054501344453672</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0007005226372892254</v>
+        <v>0.000842097225359142</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0007999463241533242</v>
+        <v>0.0005731643047648822</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0007177891635641163</v>
+        <v>0.001000466588483125</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0007941986215358019</v>
+        <v>0.001067394595769781</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0007617071721248943</v>
+        <v>0.0007441150837754157</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0007637187115954238</v>
+        <v>0.000357812280841871</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0006980925972312615</v>
+        <v>0.0008472429639236272</v>
       </c>
       <c r="R8" t="n">
-        <v>0.000490398612250806</v>
+        <v>0.0006763974342436578</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0007680448042467678</v>
+        <v>0.0005633535036812636</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0006007566308993431</v>
+        <v>0.001023039990904357</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00101444149312365</v>
+        <v>0.000585181825103752</v>
       </c>
       <c r="V8" t="n">
-        <v>0.000973315813485916</v>
+        <v>0.0003803149267013431</v>
       </c>
       <c r="W8" t="n">
-        <v>0.000738930342627942</v>
+        <v>0.0007053100760287229</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0007021602562011593</v>
+        <v>0.0006113440541453191</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0005588246258277377</v>
+        <v>0.0009335582804571521</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.000736140014020357</v>
+        <v>0.0009428906239314732</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0006363807675854616</v>
+        <v>0.000891614526993382</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0007331224627604524</v>
+        <v>0.0007737873618162792</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0007379022723532234</v>
+        <v>0.0008691827846177127</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0008227020568564588</v>
+        <v>0.0009947999568604446</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0007591934987645124</v>
+        <v>0.0005918110955092471</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0007227529172012647</v>
+        <v>0.001129995531697361</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0007664909792658903</v>
+        <v>0.0009089271378067144</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0007280734759209313</v>
+        <v>0.0006618781122874929</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0007430892353593677</v>
+        <v>0.001102605388902334</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0007436474286816025</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.0008330970540029113</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0.001404358755389437</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.0008795857330529143</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.000910090999087875</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.000801953258265424</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0.0008507506586479025</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.0007180848576452959</v>
+        <v>0.0009288063845712686</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0005981195058979399</v>
+        <v>0.001253088501110642</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0005483356225501342</v>
+        <v>0.0008548684467236245</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0003393564597925803</v>
+        <v>0.001111861626152161</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0005154430113978832</v>
+        <v>0.001119772856909597</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0006446573411350306</v>
+        <v>0.0009230397684784733</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000404398012055835</v>
+        <v>0.0005454023325754224</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0008086919310190328</v>
+        <v>0.000744577828985782</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0006145091222425304</v>
+        <v>0.0009367696716335135</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0004299161328028907</v>
+        <v>0.001271967002152866</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002442406414673536</v>
+        <v>0.0009902464822685727</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0004492634699191919</v>
+        <v>0.001168313376527375</v>
       </c>
       <c r="N9" t="n">
-        <v>0.000648132755751941</v>
+        <v>0.001355811606869496</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0004270397619503064</v>
+        <v>0.0009379712581657044</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0005103022472560053</v>
+        <v>0.0007017772139845397</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0006488129177825734</v>
+        <v>0.001184599679287839</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0005733229279495651</v>
+        <v>0.001065243985443728</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0003345889721166232</v>
+        <v>0.001026310682399229</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0007783674862892096</v>
+        <v>0.001067113605527242</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0006418005769586065</v>
+        <v>0.00109658645362263</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0008167585912593748</v>
+        <v>0.0008417383982772643</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0006068921762979061</v>
+        <v>0.001136823001685976</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0005203563460872971</v>
+        <v>0.001019505306869893</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0007474693145477768</v>
+        <v>0.001434565137039761</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0006272151861544187</v>
+        <v>0.001250114940201338</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0005333924014792592</v>
+        <v>0.001167380686941241</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0006050886785540557</v>
+        <v>0.001245984251113179</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0004615411033216131</v>
+        <v>0.001203800523538596</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0007772115090934102</v>
+        <v>0.001199325851172669</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0007221756201088336</v>
+        <v>0.0009535600616615847</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0005602636521006019</v>
+        <v>0.001227669806558897</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0006463585735761108</v>
+        <v>0.001410614924707902</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0005649971609448657</v>
+        <v>0.001067727431068909</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0006007118241196243</v>
+        <v>0.001290442640298512</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0003696782898179258</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.0006178366526276945</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0.001404358755389437</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.000763403346168117</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.0008403883344662393</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.0006277154221690968</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.0006076333756878668</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.0006342264418206498</v>
+        <v>0.001205918431453031</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0005655838624190898</v>
+        <v>0.0009675375720748951</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0006176551995779067</v>
+        <v>0.0007644850847827463</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000686189974055562</v>
+        <v>0.0006683875157843823</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0005328518070610137</v>
+        <v>0.0006226857540029346</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0005408439501383759</v>
+        <v>0.0004084122484917781</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005835391607539858</v>
+        <v>0.0007475274411736167</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0009925373762933148</v>
+        <v>0.0005054501344453672</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0006145091222425304</v>
+        <v>0.0009367696716335135</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0005746112382308075</v>
+        <v>0.0007221538417850958</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0006271592821887834</v>
+        <v>0.0004954216748120118</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0004413767253996574</v>
+        <v>0.0008293671536439614</v>
       </c>
       <c r="N10" t="n">
-        <v>0.00041367104911525</v>
+        <v>0.001030575276711989</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0004543288864582782</v>
+        <v>0.0008270635440593427</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0006363894849232338</v>
+        <v>0.0005035491921825213</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0005048419966566176</v>
+        <v>0.0008751200744977201</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0007516180130092801</v>
+        <v>0.0007216857627273702</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0005364567360680229</v>
+        <v>0.0006097230137463398</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0006787343190696124</v>
+        <v>0.001252878345478825</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0005405881702010474</v>
+        <v>0.0007218092963227261</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0009783657647667086</v>
+        <v>0.0007366471144572116</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0006291547005678032</v>
+        <v>0.0006323992719430948</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0006424383294659382</v>
+        <v>0.0004735231816599286</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.001000624778174174</v>
+        <v>0.000877295916624832</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0005852961408886555</v>
+        <v>0.001007721602080114</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0006971632841634287</v>
+        <v>0.0006815279725632019</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0004070375413822185</v>
+        <v>0.0006700367527885509</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0004049079388057199</v>
+        <v>0.0006929442343859797</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0004806951162231559</v>
+        <v>0.0007733347257234103</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0005530030583348767</v>
+        <v>0.0003920860759331945</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0006386900417431043</v>
+        <v>0.0009076107722873534</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0004971789013222283</v>
+        <v>0.0009732054643194883</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0005994697547796856</v>
+        <v>0.0005973119669494136</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0004886105137697099</v>
+        <v>0.0008053613299902657</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0004586277719223314</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.0005726124338257713</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0.001152231293809118</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.0006772959867778977</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.0006800256828841852</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.0005759330160877631</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.0005997585203658582</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.0005585010269372639</v>
+        <v>0.0007798494376280642</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0006335251220954679</v>
+        <v>0.0009041756817274398</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0004453331002304017</v>
+        <v>0.001021591652926877</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0005060960148814097</v>
+        <v>0.0007183668832259168</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00056364146230816</v>
+        <v>0.0004143008832643204</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0004892009183266998</v>
+        <v>0.000706540133574218</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001904159685607467</v>
+        <v>0.001111452530874603</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0007005226372892254</v>
+        <v>0.000842097225359142</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0004299161328028907</v>
+        <v>0.001271967002152866</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0005746112382308075</v>
+        <v>0.0007221538417850958</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004212305830278609</v>
+        <v>0.0006905836304117773</v>
       </c>
       <c r="M11" t="n">
-        <v>0.000431329584137072</v>
+        <v>0.0008449817579840686</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0004607326459897391</v>
+        <v>0.0004848935844070229</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003183666867220825</v>
+        <v>0.0009254344296435385</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0005410571757002036</v>
+        <v>0.0008160709160830051</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0004669503871427328</v>
+        <v>0.0007779198924865236</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0004018926622336754</v>
+        <v>0.0008989744572111238</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0002488510694807028</v>
+        <v>0.0006186274496350462</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0005536274165241771</v>
+        <v>0.001424817821144099</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0006136047523460647</v>
+        <v>0.0006076176424986683</v>
       </c>
       <c r="V11" t="n">
-        <v>0.000756776079260617</v>
+        <v>0.0008588569711481599</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0003945101591925043</v>
+        <v>0.0001994642887308438</v>
       </c>
       <c r="X11" t="n">
-        <v>0.000261135543658617</v>
+        <v>0.0005280511638437632</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0006533456701985925</v>
+        <v>0.0005711208216584029</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0002758065159549259</v>
+        <v>0.0009694716251580032</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0002028084059740542</v>
+        <v>0.0006347174809696875</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0003962404349426933</v>
+        <v>0.0003213690326329868</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0004361486063788166</v>
+        <v>0.0007025498464296517</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0005680953219538796</v>
+        <v>0.0005589336796566843</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0004897837769554735</v>
+        <v>0.0005316216467265658</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0005481402809684762</v>
+        <v>0.0009597243116989928</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0005094130073875136</v>
+        <v>0.0006298416681338918</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0004982628653137059</v>
+        <v>0.0004334546644998082</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0004842788794533269</v>
+        <v>0.0007151249616690123</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0002627910484787949</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.0006610073276509853</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0.001238068881017549</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.0004466690121740929</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.0007221846935032954</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.0003396182315554075</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.0006232545144549837</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0.0005425832471364714</v>
+        <v>0.0005007134953452762</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0006685364665462279</v>
+        <v>0.0009607586959189257</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0006543043808557071</v>
+        <v>0.0008959486471696157</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0004352941064034891</v>
+        <v>0.000696491221404799</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0006497816490031337</v>
+        <v>0.000636147117733601</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0007524612069781442</v>
+        <v>0.0005608568754989707</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0004639010964846237</v>
+        <v>0.0007881580054687012</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0007999463241533242</v>
+        <v>0.0005731643047648822</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0002442406414673536</v>
+        <v>0.0009902464822685727</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0006271592821887834</v>
+        <v>0.0004954216748120118</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0004212305830278609</v>
+        <v>0.0006905836304117773</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0005014918274837746</v>
+        <v>0.0008127252327773824</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0007000312925878628</v>
+        <v>0.0009313677234532479</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0005401767471501532</v>
+        <v>0.0006841091536441605</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0006733754109979317</v>
+        <v>0.0007086237664902245</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0007107393139493809</v>
+        <v>0.0006438022638995937</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0006223948780496773</v>
+        <v>0.0006604456521928591</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0002668298568077362</v>
+        <v>0.000438401328834703</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0008009930923153633</v>
+        <v>0.001412896870965178</v>
       </c>
       <c r="U12" t="n">
-        <v>0.000752208816697059</v>
+        <v>0.0007623511535861873</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0006616494472846236</v>
+        <v>0.0006652223015853794</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0006439267401811194</v>
+        <v>0.0006330858675742461</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0005869226158633972</v>
+        <v>0.0005383481730170796</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0006747861147360426</v>
+        <v>0.0008062630984105689</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0006201364274058232</v>
+        <v>0.0008459026457296084</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0005417262857800503</v>
+        <v>0.0006375080949448798</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0006199101740907173</v>
+        <v>0.0006970723883175175</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0005231396849119453</v>
+        <v>0.0008243761595616136</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0008101261009444444</v>
+        <v>0.0008756847483285075</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0007310420981907263</v>
+        <v>0.0006359115810677965</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0007012286167475876</v>
+        <v>0.0008837769623915574</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0006999933530774915</v>
+        <v>0.001019371376543745</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0006261082442899926</v>
+        <v>0.0006792424553029945</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0006895172934172761</v>
+        <v>0.0008474035363521475</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.000446105240706422</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0.0007371395037430492</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0.001404358755389437</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.0007187159464830739</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0.0009480465755461292</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.0006477403157050472</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.0007510019441552301</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.0007358411122708047</v>
+        <v>0.000717109612991236</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0004405637442133486</v>
+        <v>0.0007164265981208997</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0005017517157461259</v>
+        <v>0.0007251886922089658</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0004787095603551546</v>
+        <v>0.0004442858669121244</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0003107020621736757</v>
+        <v>0.0006992421616504738</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0004014861200852862</v>
+        <v>0.0008165403075860928</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003481818123864901</v>
+        <v>0.0008154435893774109</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0007177891635641163</v>
+        <v>0.001000466588483125</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0004492634699191919</v>
+        <v>0.001168313376527375</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0004413767253996574</v>
+        <v>0.0008293671536439614</v>
       </c>
       <c r="K13" t="n">
-        <v>0.000431329584137072</v>
+        <v>0.0008449817579840686</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0005014918274837746</v>
+        <v>0.0008127252327773824</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0003948637339044377</v>
+        <v>0.0007726551044305401</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0003025182886203548</v>
+        <v>0.0007121554260459739</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0004379108029413028</v>
+        <v>0.0009524454859249392</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0004223454746699823</v>
+        <v>0.0009437362040992007</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0004904870894023259</v>
+        <v>0.001032778188192777</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0004412048307859287</v>
+        <v>0.0007769345547798252</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0004996388950869578</v>
+        <v>0.001385068548043908</v>
       </c>
       <c r="U13" t="n">
-        <v>0.000588594734216768</v>
+        <v>0.001137952397332888</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0009546058892590349</v>
+        <v>0.0009797371650301504</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0004560054312883541</v>
+        <v>0.000829906614311879</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0005071743552189616</v>
+        <v>0.0006878225508333984</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0007983176956734961</v>
+        <v>0.001192016727005298</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0004944315947321416</v>
+        <v>0.001241701867247379</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0005184272783846249</v>
+        <v>0.0003682220361423833</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0003772524056897592</v>
+        <v>0.0007634568217164316</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0002558482951078772</v>
+        <v>0.0008585375038912454</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0004938266314896644</v>
+        <v>0.0007357340446109785</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0004335391011046538</v>
+        <v>0.000810283904794849</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0004156890936908</v>
+        <v>0.0008004595497682417</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0003936183317501539</v>
+        <v>0.001317369601383706</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0005528949263060645</v>
+        <v>0.0009248843666296036</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.000402127896269928</v>
+        <v>0.0004429517257716925</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0003213001562179975</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0.0004820084933105049</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0.001325024860954808</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.0007418677599864022</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0.0006624929569060341</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.0005745963134237983</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.0004740218697547196</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0.0004109063483280628</v>
+        <v>0.0006731562889613747</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0004779495766345493</v>
+        <v>0.0009459675945561783</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0005107235582205779</v>
+        <v>0.001097266362573354</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0006289511202645262</v>
+        <v>0.0008239194027629364</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0004215532370601625</v>
+        <v>0.0006530788503909997</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0002330699275102463</v>
+        <v>0.0009234240083482138</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0004479445907162552</v>
+        <v>0.001192601733130086</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0007941986215358019</v>
+        <v>0.001067394595769781</v>
       </c>
       <c r="I14" t="n">
-        <v>0.000648132755751941</v>
+        <v>0.001355811606869496</v>
       </c>
       <c r="J14" t="n">
-        <v>0.00041367104911525</v>
+        <v>0.001030575276711989</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0004607326459897391</v>
+        <v>0.0004848935844070229</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0007000312925878628</v>
+        <v>0.0009313677234532479</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0003948637339044377</v>
+        <v>0.0007726551044305401</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0003317186273278899</v>
+        <v>0.0009587343336704192</v>
       </c>
       <c r="P14" t="n">
-        <v>0.000502135324491182</v>
+        <v>0.001032184839681787</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0002149653375441975</v>
+        <v>0.0009030609776827146</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0005443291862924506</v>
+        <v>0.001098056193236197</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0005397630914803651</v>
+        <v>0.0007671228084368502</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0004176288154587599</v>
+        <v>0.001447603141072797</v>
       </c>
       <c r="U14" t="n">
-        <v>0.00054691738219812</v>
+        <v>0.0008730925038819337</v>
       </c>
       <c r="V14" t="n">
-        <v>0.001050109097121933</v>
+        <v>0.0009546521387856736</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0005125641828381643</v>
+        <v>0.0005616305857921192</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0004481492496757579</v>
+        <v>0.0007762935118121504</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0009218414735617835</v>
+        <v>0.0008951048733522027</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.000413154648676692</v>
+        <v>0.001122880750785851</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0005111994876537149</v>
+        <v>0.000665132169517861</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0001941528010848316</v>
+        <v>0.0005702048693322614</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0003182475502812896</v>
+        <v>0.0009289983221337659</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0001792498488964726</v>
+        <v>0.0006264969797449985</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0003363350822918965</v>
+        <v>0.0008266771603964475</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0004593962650052962</v>
+        <v>0.001083177560109592</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0002695496386098832</v>
+        <v>0.0008985019451093419</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.00045656011853653</v>
+        <v>0.0007319617459799612</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0002478179808500987</v>
+        <v>0.0007469040075734959</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0003637883854206484</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0.0004967011451134498</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0.001117573015456794</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.0005415157124515794</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0.0003963930482713133</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.00042235654907804</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0.0004740586013895055</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0.0002681119536849518</v>
+        <v>0.0006352440161852192</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.000480605610652216</v>
+        <v>0.0009582409772063966</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0003378908904315715</v>
+        <v>0.0008228231178222704</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0004662107924246352</v>
+        <v>0.0007010370037059213</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000321387619036637</v>
+        <v>0.00074772921553591</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0002819268612039545</v>
+        <v>0.0007668528724721626</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0002601795587123893</v>
+        <v>0.0008405120830800404</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0007617071721248943</v>
+        <v>0.0007441150837754157</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0004270397619503064</v>
+        <v>0.0009379712581657044</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0004543288864582782</v>
+        <v>0.0008270635440593427</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0003183666867220825</v>
+        <v>0.0009254344296435385</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0005401767471501532</v>
+        <v>0.0006841091536441605</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0003025182886203548</v>
+        <v>0.0007121554260459739</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0003317186273278899</v>
+        <v>0.0009587343336704192</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.000319102144247842</v>
+        <v>0.00086695788819347</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0003146939669453053</v>
+        <v>0.0005114167105283794</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0004400155126258569</v>
+        <v>0.0006842081805678906</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0003969729739244409</v>
+        <v>0.0005946167108253832</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0005108625029629158</v>
+        <v>0.001148637155516392</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0004531370050443574</v>
+        <v>0.0009119635217276142</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0009698692965332378</v>
+        <v>0.000599961842177001</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0004071502281617778</v>
+        <v>0.0008201555645949737</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0003110942909860199</v>
+        <v>0.0007839662120705202</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0008144250260061311</v>
+        <v>0.001065588595362737</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0003965041053030695</v>
+        <v>0.000895860258567893</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0004090109815816448</v>
+        <v>0.000731578850734094</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.000315844577539978</v>
+        <v>0.0007735772241946801</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0002851706878872673</v>
+        <v>0.0009656880754145106</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0004572130831065231</v>
+        <v>0.001026713877194907</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.000469600750816369</v>
+        <v>0.0008981584393088136</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0003449491240806433</v>
+        <v>0.0009740648987416037</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.000399833866154808</v>
+        <v>0.001217969407376425</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0004354400254736981</v>
+        <v>0.0009831815644797842</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0002840457914687201</v>
+        <v>0.0009004918617120355</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0001828279432995404</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0.00044019876233142</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0.001215611854148644</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.0006074597395443141</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0.0005573943162675215</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.0003995981077105706</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0.0003838916299711895</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0.0003628859048749979</v>
+        <v>0.0007749647701224175</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0004405813052204726</v>
+        <v>0.0009488099202462937</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000351766459577166</v>
+        <v>0.0006660478140725422</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0004663721258220573</v>
+        <v>0.0008186550815920069</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000232405269837704</v>
+        <v>0.0007635220383634159</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0003804020120800849</v>
+        <v>0.0004418224608108516</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004698945443488867</v>
+        <v>0.000690041325737788</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0007637187115954238</v>
+        <v>0.000357812280841871</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0005103022472560053</v>
+        <v>0.0007017772139845397</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0006363894849232338</v>
+        <v>0.0005035491921825213</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0005410571757002036</v>
+        <v>0.0008160709160830051</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0006733754109979317</v>
+        <v>0.0007086237664902245</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0004379108029413028</v>
+        <v>0.0009524454859249392</v>
       </c>
       <c r="N16" t="n">
-        <v>0.000502135324491182</v>
+        <v>0.001032184839681787</v>
       </c>
       <c r="O16" t="n">
-        <v>0.000319102144247842</v>
+        <v>0.00086695788819347</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0004362585905493496</v>
+        <v>0.001019782005069676</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0004285245901303541</v>
+        <v>0.0009077213126475533</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0005844224022624835</v>
+        <v>0.0007291217518744709</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0005558015955871807</v>
+        <v>0.0009753079002671997</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0004628336049005554</v>
+        <v>0.0007209284756513712</v>
       </c>
       <c r="V16" t="n">
-        <v>0.001158725747136685</v>
+        <v>0.0006102761396954394</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0005119902581963594</v>
+        <v>0.0006708856465025473</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0004347781392849886</v>
+        <v>0.0004964845855714546</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0009367423869890423</v>
+        <v>0.001025245534061839</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0006495591950021386</v>
+        <v>0.001112761650934075</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0005510897091478112</v>
+        <v>0.0008884164573648381</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0005129841868135675</v>
+        <v>0.0008002655683893652</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0003994761968719064</v>
+        <v>0.0007189222113423455</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0006027805769340739</v>
+        <v>0.0008890720220999373</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.000630861376591514</v>
+        <v>0.0004248106488260604</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0001976394164531438</v>
+        <v>0.001014559655288048</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.000484339174780054</v>
+        <v>0.0009430395221161433</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.000464913071532706</v>
+        <v>0.0005687230504021491</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0003331274650229183</v>
+        <v>0.001010609850550161</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0004182283964566908</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0.0003184323151178643</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0.001291860368962209</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.0008249673673920596</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0.000541561460560792</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0.0006448963669467978</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0.0001814147696005705</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0.0003645015399805935</v>
+        <v>0.0008612354013947929</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0004113330945082985</v>
+        <v>0.001129436336123301</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0004913508447900556</v>
+        <v>0.001130755305052761</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0005573858045588926</v>
+        <v>0.000852290862430361</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0003792270433418355</v>
+        <v>0.0006858284599595559</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0002317659509750783</v>
+        <v>0.0008712683043069192</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004642458137531928</v>
+        <v>0.001132767161585928</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0006980925972312615</v>
+        <v>0.0008472429639236272</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0006488129177825734</v>
+        <v>0.001184599679287839</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0005048419966566176</v>
+        <v>0.0008751200744977201</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0004669503871427328</v>
+        <v>0.0007779198924865236</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0007107393139493809</v>
+        <v>0.0006438022638995937</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0004223454746699823</v>
+        <v>0.0009437362040992007</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0002149653375441975</v>
+        <v>0.0009030609776827146</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0003146939669453053</v>
+        <v>0.0005114167105283794</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0004362585905493496</v>
+        <v>0.001019782005069676</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0004737660397546512</v>
+        <v>0.0006094830583196198</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0005408322037616236</v>
+        <v>0.0005320899902801032</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0003766066867005111</v>
+        <v>0.001369904305491893</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0005802151706519621</v>
+        <v>0.0007515371900115335</v>
       </c>
       <c r="V17" t="n">
-        <v>0.00107348239483261</v>
+        <v>0.0007331291738229171</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0005382333003565628</v>
+        <v>0.0007156542029885239</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0004075218958816414</v>
+        <v>0.0008644138241034571</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.0008656681770207828</v>
+        <v>0.0007593223970999713</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0004524306881438362</v>
+        <v>0.000675813906431279</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0005060271939307514</v>
+        <v>0.0008044741334036743</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.000186931180943247</v>
+        <v>0.0006560098832237845</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0003137031432597328</v>
+        <v>0.001010953855064241</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0002646670143657531</v>
+        <v>0.0009938174405712569</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.00042960052547934</v>
+        <v>0.0009309378656502754</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0004156803650866203</v>
+        <v>0.001081636348504677</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0003588118817553789</v>
+        <v>0.00101315323263496</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.0003627381835115278</v>
+        <v>0.0009474972651559398</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0001592867591250723</v>
+        <v>0.000961619739424775</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0003681632048391821</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0.0004226588315998742</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0.00111272331370253</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0.0005821655307279151</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0.0004436200722629566</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0.0004314107759993923</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0.0004325807878923427</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0.0002595290245289932</v>
+        <v>0.0007570042972418417</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.000565230667631836</v>
+        <v>0.001320267482587458</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0004530497930058533</v>
+        <v>0.001177183122650688</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004723102215005988</v>
+        <v>0.0009860858573805518</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0004939252818476571</v>
+        <v>0.0007927086117564957</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0004794574555122073</v>
+        <v>0.000676279148038398</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0003855395128337185</v>
+        <v>0.001077209297632051</v>
       </c>
       <c r="H18" t="n">
-        <v>0.000490398612250806</v>
+        <v>0.0006763974342436578</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0005733229279495651</v>
+        <v>0.001065243985443728</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0007516180130092801</v>
+        <v>0.0007216857627273702</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0004018926622336754</v>
+        <v>0.0008989744572111238</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0006223948780496773</v>
+        <v>0.0006604456521928591</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0004904870894023259</v>
+        <v>0.001032778188192777</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0005443291862924506</v>
+        <v>0.001098056193236197</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0004400155126258569</v>
+        <v>0.0006842081805678906</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0004285245901303541</v>
+        <v>0.0009077213126475533</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0004737660397546512</v>
+        <v>0.0006094830583196198</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0005274439988398422</v>
+        <v>0.0006107807916105464</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0003848573390953386</v>
+        <v>0.001399096853193115</v>
       </c>
       <c r="U18" t="n">
-        <v>0.000693222896744801</v>
+        <v>0.0006255569951477722</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0009916872355191699</v>
+        <v>0.0006354381444387483</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0003928963361548954</v>
+        <v>0.000836487030112312</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0003300738428901062</v>
+        <v>0.0009330386918204595</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.0006826787479145303</v>
+        <v>0.0008817747826230647</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.0005169109430184371</v>
+        <v>0.000677331116736244</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0003078214618051075</v>
+        <v>0.0008620198522196764</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.0005148347503255532</v>
+        <v>0.0007865417903257894</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0005038601756706817</v>
+        <v>0.001162359489990121</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0006236736829738802</v>
+        <v>0.001035777802060781</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0005267769518400164</v>
+        <v>0.0008625799906693646</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0004435478183797252</v>
+        <v>0.001254128750441704</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.0005417707065536668</v>
+        <v>0.001041117080433517</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.0005062011638943684</v>
+        <v>0.000865639127302414</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.0004780263234387109</v>
+        <v>0.001103946535114222</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.0004704460986705548</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0.0005675849860141527</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0.001299925148651584</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0.0006837405462107979</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0.0006781976894288574</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0.0005886075958012556</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0.0005409337387696236</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0.0004861026534371755</v>
+        <v>0.0009891115566372872</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0005839289458934497</v>
+        <v>0.001060782537431346</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0005382599388982408</v>
+        <v>0.0009653077411581449</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0004520495433414003</v>
+        <v>0.000789996637514659</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0005714601032018018</v>
+        <v>0.0006540611711085323</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0006097709480915672</v>
+        <v>0.0005394600106560362</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003510383297166774</v>
+        <v>0.0009106047193295413</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0007680448042467678</v>
+        <v>0.0005633535036812636</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0003345889721166232</v>
+        <v>0.001026310682399229</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0005364567360680229</v>
+        <v>0.0006097230137463398</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0002488510694807028</v>
+        <v>0.0006186274496350462</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0002668298568077362</v>
+        <v>0.000438401328834703</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0004412048307859287</v>
+        <v>0.0007769345547798252</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0005397630914803651</v>
+        <v>0.0007671228084368502</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0003969729739244409</v>
+        <v>0.0005946167108253832</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0005844224022624835</v>
+        <v>0.0007291217518744709</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0005408322037616236</v>
+        <v>0.0005320899902801032</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0005274439988398422</v>
+        <v>0.0006107807916105464</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0006803962473860342</v>
+        <v>0.001265440099792964</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0006496979481374108</v>
+        <v>0.0005905467827745863</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0007110076897115061</v>
+        <v>0.0005511916683741434</v>
       </c>
       <c r="W19" t="n">
-        <v>0.0005552349506061257</v>
+        <v>0.000557136055997562</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0004228448670386825</v>
+        <v>0.0006085562313006678</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.0006940776081339585</v>
+        <v>0.0007940700159654366</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.0004641237727899828</v>
+        <v>0.0008996310764838319</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.0004034594980463513</v>
+        <v>0.0005586628643860192</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.0004410759013792641</v>
+        <v>0.0005391786009007722</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.0003990855166946862</v>
+        <v>0.0008701370920115414</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.0006544916258592041</v>
+        <v>0.0007650890176628551</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.0006159250021141045</v>
+        <v>0.0006747082387983073</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.0006084719200472156</v>
+        <v>0.001080475589791118</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.0005754466995528252</v>
+        <v>0.0008841895394873316</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.0004585945586937011</v>
+        <v>0.0006917345436792987</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.0005323139220321279</v>
+        <v>0.0008789444057889219</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.0002805225905764345</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0.0006561656814450122</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0.001298031303712368</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0.0005416764193828122</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0.000810283016877101</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0.0004594149476663624</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0.0006528432216315915</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0.0006028779114326427</v>
+        <v>0.0007629987749471919</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0005739378765271104</v>
+        <v>0.001353282205319402</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0005515231002359244</v>
+        <v>0.001037715403188717</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0006786825681856127</v>
+        <v>0.001336668618547091</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0005250204991308747</v>
+        <v>0.001356402818667449</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0003961888050642167</v>
+        <v>0.001128016612228058</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0005483133721319726</v>
+        <v>0.001227693073203228</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0006007566308993431</v>
+        <v>0.001023039990904357</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0007783674862892096</v>
+        <v>0.001067113605527242</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0006787343190696124</v>
+        <v>0.001252878345478825</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0005536274165241771</v>
+        <v>0.001424817821144099</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0008009930923153633</v>
+        <v>0.001412896870965178</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0004996388950869578</v>
+        <v>0.001385068548043908</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0004176288154587599</v>
+        <v>0.001447603141072797</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0005108625029629158</v>
+        <v>0.001148637155516392</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0005558015955871807</v>
+        <v>0.0009753079002671997</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0003766066867005111</v>
+        <v>0.001369904305491893</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0003848573390953386</v>
+        <v>0.001399096853193115</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0006803962473860342</v>
+        <v>0.001265440099792964</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0007200784196369826</v>
+        <v>0.001231970881381171</v>
       </c>
       <c r="V20" t="n">
-        <v>0.001113189751538055</v>
+        <v>0.001018025411760134</v>
       </c>
       <c r="W20" t="n">
-        <v>0.0004575636542401925</v>
+        <v>0.001282824801811867</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0004772026701107659</v>
+        <v>0.001203967179454703</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.0008271011210761801</v>
+        <v>0.001521406546636798</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.0005269794780601615</v>
+        <v>0.001513217771828066</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.0004974326529640028</v>
+        <v>0.001454953044087533</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.0004293485183858439</v>
+        <v>0.001281007856925812</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.0005293857363916509</v>
+        <v>0.001207930673568518</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.0004014372396141742</v>
+        <v>0.00145803833071718</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.0003266839613341432</v>
+        <v>0.001214814162520163</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0005350306033455841</v>
+        <v>0.001512803727430764</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.0004796007022036646</v>
+        <v>0.001341641003077921</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.0005981295522392638</v>
+        <v>0.001331752685042642</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.0004423545396138253</v>
+        <v>0.001515560371552579</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.0005883258631910845</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0.0005617154385092176</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0.001141188416098326</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0.0006729581843660156</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0.0005811778551751559</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0.0006298223230030076</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0.0005730557844268713</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0.0004534808355022137</v>
+        <v>0.001379919771193928</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0007251039804901657</v>
+        <v>0.001269677294427742</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0003227188235878585</v>
+        <v>0.001165827692216639</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0007701730805420575</v>
+        <v>0.001033872423080682</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0005500828560460604</v>
+        <v>0.0007020735230559538</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0005175556892136132</v>
+        <v>0.0006146563129275769</v>
       </c>
       <c r="G21" t="n">
-        <v>0.000588681216164441</v>
+        <v>0.001165519423109031</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00101444149312365</v>
+        <v>0.000585181825103752</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0006418005769586065</v>
+        <v>0.00109658645362263</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0005405881702010474</v>
+        <v>0.0007218092963227261</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0006136047523460647</v>
+        <v>0.0006076176424986683</v>
       </c>
       <c r="L21" t="n">
-        <v>0.000752208816697059</v>
+        <v>0.0007623511535861873</v>
       </c>
       <c r="M21" t="n">
-        <v>0.000588594734216768</v>
+        <v>0.001137952397332888</v>
       </c>
       <c r="N21" t="n">
-        <v>0.00054691738219812</v>
+        <v>0.0008730925038819337</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0004531370050443574</v>
+        <v>0.0009119635217276142</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0004628336049005554</v>
+        <v>0.0007209284756513712</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0005802151706519621</v>
+        <v>0.0007515371900115335</v>
       </c>
       <c r="R21" t="n">
-        <v>0.000693222896744801</v>
+        <v>0.0006255569951477722</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0006496979481374108</v>
+        <v>0.0005905467827745863</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0007200784196369826</v>
+        <v>0.001231970881381171</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.001147212557189824</v>
+        <v>0.0006105671814859486</v>
       </c>
       <c r="W21" t="n">
-        <v>0.0005212769565607131</v>
+        <v>0.0005270775066453529</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0005235412596240859</v>
+        <v>0.0007852548048621934</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.001129358453254761</v>
+        <v>0.0006570100731427152</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.0006325847687807131</v>
+        <v>0.000833435242153116</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.0006427524648391483</v>
+        <v>0.0009225983913092079</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.0005657109787431769</v>
+        <v>0.0005711613185130872</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.000580727862297444</v>
+        <v>0.0009862260484851432</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.0005998237926891607</v>
+        <v>0.0008512832125168386</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.0006835280912931787</v>
+        <v>0.0006573632341979451</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0004507090841551163</v>
+        <v>0.001300102867372314</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.0004944755697457779</v>
+        <v>0.0005442553122982906</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.0006599562516612739</v>
+        <v>0.0005783304184430297</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.0004848779459640465</v>
+        <v>0.001116116977340893</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.0005295724630322093</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0.0006131958051695242</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0.001147212557189824</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0.0007553069501518017</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0.0005995069945716947</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0.0006213649674098064</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0.0004160883888710267</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0.0005624374865160486</v>
+        <v>0.0008974312071261733</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001126660024246718</v>
+        <v>0.001127254917991796</v>
       </c>
       <c r="C22" t="n">
-        <v>0.001065647743215086</v>
+        <v>0.0009002667019520666</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0009301244367438554</v>
+        <v>0.0009374861831184352</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001140738540474155</v>
+        <v>0.00083131793327742</v>
       </c>
       <c r="F22" t="n">
-        <v>0.001119241076217913</v>
+        <v>0.0004980749039133301</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0008212289531392531</v>
+        <v>0.0008890931404579569</v>
       </c>
       <c r="H22" t="n">
-        <v>0.000973315813485916</v>
+        <v>0.0003803149267013431</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0008167585912593748</v>
+        <v>0.0008417383982772643</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0009783657647667086</v>
+        <v>0.0007366471144572116</v>
       </c>
       <c r="K22" t="n">
-        <v>0.000756776079260617</v>
+        <v>0.0008588569711481599</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0006616494472846236</v>
+        <v>0.0006652223015853794</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0009546058892590349</v>
+        <v>0.0009797371650301504</v>
       </c>
       <c r="N22" t="n">
-        <v>0.001050109097121933</v>
+        <v>0.0009546521387856736</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0009698692965332378</v>
+        <v>0.000599961842177001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.001158725747136685</v>
+        <v>0.0006102761396954394</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.00107348239483261</v>
+        <v>0.0007331291738229171</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0009916872355191699</v>
+        <v>0.0006354381444387483</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0007110076897115061</v>
+        <v>0.0005511916683741434</v>
       </c>
       <c r="T22" t="n">
-        <v>0.001113189751538055</v>
+        <v>0.001018025411760134</v>
       </c>
       <c r="U22" t="n">
-        <v>0.001147212557189824</v>
+        <v>0.0006105671814859486</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.0009679260775048903</v>
+        <v>0.0007415997827247189</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0009379663002226349</v>
+        <v>0.0007392267022367544</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.0006008481436344805</v>
+        <v>0.0009408225589306449</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.0008080406025147337</v>
+        <v>0.0008272986197333307</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.0008288522886389205</v>
+        <v>0.0009068941507796238</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.0009730546772737447</v>
+        <v>0.0007553851604216856</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.0009875153739988545</v>
+        <v>0.000984211648916536</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001112919918296517</v>
+        <v>0.001068985995610555</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.001013149938244557</v>
+        <v>0.0007802087150548017</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.001157524674893792</v>
+        <v>0.001192512419575825</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.001080994758042145</v>
+        <v>0.0009441604981594651</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.001022155043537439</v>
+        <v>0.0007800681668697629</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.001111471016422675</v>
+        <v>0.001137561387852283</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.0008684720393662696</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0.001220063840911742</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0.001404358755389437</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0.0007986312118106517</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0.001284143117127959</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0.0008333907299767398</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0.001233067413130983</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0.001144008534161368</v>
+        <v>0.000927523343817744</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.000734388213855064</v>
+        <v>0.00085158425319275</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0003128964621205048</v>
+        <v>0.0009119101296241693</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0006881429497859296</v>
+        <v>0.0006561334132534017</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0005731914097575591</v>
+        <v>0.0003430664060436905</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0004722776063476197</v>
+        <v>0.0006213449526627652</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000353845922369856</v>
+        <v>0.001009971971652721</v>
       </c>
       <c r="H23" t="n">
-        <v>0.000738930342627942</v>
+        <v>0.0007053100760287229</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0006068921762979061</v>
+        <v>0.001136823001685976</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0006291547005678032</v>
+        <v>0.0006323992719430948</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0003945101591925043</v>
+        <v>0.0001994642887308438</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0006439267401811194</v>
+        <v>0.0006330858675742461</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0004560054312883541</v>
+        <v>0.000829906614311879</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0005125641828381643</v>
+        <v>0.0005616305857921192</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0004071502281617778</v>
+        <v>0.0008201555645949737</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0005119902581963594</v>
+        <v>0.0006708856465025473</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0005382333003565628</v>
+        <v>0.0007156542029885239</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0003928963361548954</v>
+        <v>0.000836487030112312</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0005552349506061257</v>
+        <v>0.000557136055997562</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0004575636542401925</v>
+        <v>0.001282824801811867</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0005212769565607131</v>
+        <v>0.0005270775066453529</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0009679260775048903</v>
+        <v>0.0007415997827247189</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0003601394173024194</v>
+        <v>0.0004274467432404244</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.0008265818492362045</v>
+        <v>0.0005786484753238335</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.0003884971536111267</v>
+        <v>0.0009141682967336926</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.0003456522747666553</v>
+        <v>0.0006466014036413121</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.0005068851263572613</v>
+        <v>0.0003079097425377763</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.0005643482003673111</v>
+        <v>0.0006218088982638105</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.0005655303400740068</v>
+        <v>0.000591062312088131</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.0004528928135599693</v>
+        <v>0.0004357866688857666</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.000482575141475442</v>
+        <v>0.000906752573306245</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.0004819684638156054</v>
+        <v>0.0006284112970857754</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.0006914497603056169</v>
+        <v>0.0003974665842101713</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.0005283051255152429</v>
+        <v>0.0007302904974659164</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0004769166529698889</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0.0006809842707279205</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0.00121476054647129</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0.0006364220672604184</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0.000692446519567742</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0.0005252177954979158</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0.0005669017506568095</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0.0005706793862412822</v>
+        <v>0.0004462503027506646</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0006342108497116561</v>
+        <v>0.000614790489828897</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0002967896095166707</v>
+        <v>0.0006042601173090152</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0005462222857390461</v>
+        <v>0.0004863532518594072</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0005288076292149178</v>
+        <v>0.0005082118002048126</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0004032311594832829</v>
+        <v>0.0005063556759874301</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0003083164064991587</v>
+        <v>0.0007642372380449213</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0007021602562011593</v>
+        <v>0.0006113440541453191</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0005203563460872971</v>
+        <v>0.001019505306869893</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0006424383294659382</v>
+        <v>0.0004735231816599286</v>
       </c>
       <c r="K24" t="n">
-        <v>0.000261135543658617</v>
+        <v>0.0005280511638437632</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0005869226158633972</v>
+        <v>0.0005383481730170796</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0005071743552189616</v>
+        <v>0.0006878225508333984</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0004481492496757579</v>
+        <v>0.0007762935118121504</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0003110942909860199</v>
+        <v>0.0007839662120705202</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0004347781392849886</v>
+        <v>0.0004964845855714546</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0004075218958816414</v>
+        <v>0.0008644138241034571</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0003300738428901062</v>
+        <v>0.0009330386918204595</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0004228448670386825</v>
+        <v>0.0006085562313006678</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0004772026701107659</v>
+        <v>0.001203967179454703</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0005235412596240859</v>
+        <v>0.0007852548048621934</v>
       </c>
       <c r="V24" t="n">
-        <v>0.0009379663002226349</v>
+        <v>0.0007392267022367544</v>
       </c>
       <c r="W24" t="n">
-        <v>0.0003601394173024194</v>
+        <v>0.0004274467432404244</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.0007630630067017168</v>
+        <v>0.0008233722838410008</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.0003584216363828414</v>
+        <v>0.001063489951432138</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.0002166743496841912</v>
+        <v>0.0006185918119647924</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.0004189078919404024</v>
+        <v>0.0005424151211972944</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.0004893970125555967</v>
+        <v>0.0004009974240915531</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.0005314107545781136</v>
+        <v>0.0007238609769096287</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.0005010804876427543</v>
+        <v>0.000372092469684801</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0004607363494101854</v>
+        <v>0.0007058422577162195</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.0005009708213563308</v>
+        <v>0.0008930610793850243</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.0004559603338713814</v>
+        <v>0.0005024030190695118</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.0004138307109880311</v>
+        <v>0.0006793965809451899</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.0003584685698741946</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0.0005933797899873454</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0.001158893716539277</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0.0004783161688815617</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>0.0006194939211948156</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0.0003788509272640141</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0.0005210329363511057</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0.0004871130194666149</v>
+        <v>0.0004996591750649421</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0009019549561920089</v>
+        <v>0.001158886898265506</v>
       </c>
       <c r="C25" t="n">
-        <v>0.000940578647230899</v>
+        <v>0.00126721564878036</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0006754061655669845</v>
+        <v>0.0009817676313937827</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0009206542484666157</v>
+        <v>0.0006637867445613288</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0009125015568296976</v>
+        <v>0.0008993779121150222</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0006738441109099467</v>
+        <v>0.001342615308287884</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0005588246258277377</v>
+        <v>0.0009335582804571521</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0007474693145477768</v>
+        <v>0.001434565137039761</v>
       </c>
       <c r="J25" t="n">
-        <v>0.001000624778174174</v>
+        <v>0.000877295916624832</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0006533456701985925</v>
+        <v>0.0005711208216584029</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0006747861147360426</v>
+        <v>0.0008062630984105689</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0007983176956734961</v>
+        <v>0.001192016727005298</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0009218414735617835</v>
+        <v>0.0008951048733522027</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0008144250260061311</v>
+        <v>0.001065588595362737</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0009367423869890423</v>
+        <v>0.001025245534061839</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0008656681770207828</v>
+        <v>0.0007593223970999713</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0006826787479145303</v>
+        <v>0.0008817747826230647</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0006940776081339585</v>
+        <v>0.0007940700159654366</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0008271011210761801</v>
+        <v>0.001521406546636798</v>
       </c>
       <c r="U25" t="n">
-        <v>0.001129358453254761</v>
+        <v>0.0006570100731427152</v>
       </c>
       <c r="V25" t="n">
-        <v>0.0006008481436344805</v>
+        <v>0.0009408225589306449</v>
       </c>
       <c r="W25" t="n">
-        <v>0.0008265818492362045</v>
+        <v>0.0005786484753238335</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0007630630067017168</v>
+        <v>0.0008233722838410008</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.0007247921357270901</v>
+        <v>0.0006965779164615616</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.0006629435679669607</v>
+        <v>0.0009973476617946603</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.0008463383741974387</v>
+        <v>0.0006050613532669672</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.000841221249126988</v>
+        <v>0.0008954729043457198</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.0009819442503802851</v>
+        <v>0.0009928560734641812</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.0008462279346763411</v>
+        <v>0.0008428723966240696</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.0009557220143431017</v>
+        <v>0.00110309392018559</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.00097294385714458</v>
+        <v>0.0006086969357545764</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.0008551905405819954</v>
+        <v>0.0007638966299073407</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.000929926837269858</v>
+        <v>0.001066833810633681</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.0007686412718062912</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0.0009853710171968443</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0.001404358755389437</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0.0008225917198983994</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0.001133216460475571</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0.0007917473588530395</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.001049142094754232</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.0009447162758951851</v>
+        <v>0.0007474418952926169</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0007393416189674431</v>
+        <v>0.001308226828174105</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0005031510427692111</v>
+        <v>0.001298516794023601</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0006931667545555864</v>
+        <v>0.001069114891990158</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0006507739989616225</v>
+        <v>0.0008314665453449499</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0004485820512320572</v>
+        <v>0.0009845883985982859</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0002988397306103557</v>
+        <v>0.001268025510384339</v>
       </c>
       <c r="H26" t="n">
-        <v>0.000736140014020357</v>
+        <v>0.0009428906239314732</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0006272151861544187</v>
+        <v>0.001250114940201338</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0005852961408886555</v>
+        <v>0.001007721602080114</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0002758065159549259</v>
+        <v>0.0009694716251580032</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0006201364274058232</v>
+        <v>0.0008459026457296084</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0004944315947321416</v>
+        <v>0.001241701867247379</v>
       </c>
       <c r="N26" t="n">
-        <v>0.000413154648676692</v>
+        <v>0.001122880750785851</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0003965041053030695</v>
+        <v>0.000895860258567893</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0006495591950021386</v>
+        <v>0.001112761650934075</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0004524306881438362</v>
+        <v>0.000675813906431279</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0005169109430184371</v>
+        <v>0.000677331116736244</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0004641237727899828</v>
+        <v>0.0008996310764838319</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0005269794780601615</v>
+        <v>0.001513217771828066</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0006325847687807131</v>
+        <v>0.000833435242153116</v>
       </c>
       <c r="V26" t="n">
-        <v>0.0008080406025147337</v>
+        <v>0.0008272986197333307</v>
       </c>
       <c r="W26" t="n">
-        <v>0.0003884971536111267</v>
+        <v>0.0009141682967336926</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0003584216363828414</v>
+        <v>0.001063489951432138</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.0007247921357270901</v>
+        <v>0.0006965779164615616</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.0003131429639269767</v>
+        <v>0.001125237367763411</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.000378483083847961</v>
+        <v>0.0009181431411320484</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.0005298194724192509</v>
+        <v>0.00120569501645554</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.0004625834040234267</v>
+        <v>0.001241157417786165</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.0004208522212843489</v>
+        <v>0.001058817886749028</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0006004633353870325</v>
+        <v>0.001186495732728137</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.0004680291542885329</v>
+        <v>0.001074675329436485</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.0006238812427349842</v>
+        <v>0.001019661416585284</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.0005082265179804107</v>
+        <v>0.001231952961150151</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.0003848523607486541</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0.0007562359211291116</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0.001139788038290065</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0.000386923745288981</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0.0006749650440321886</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0.0002496947908462402</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0.000693666510439437</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0.0005551214085929344</v>
+        <v>0.0009395655397142416</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.000697008349240889</v>
+        <v>0.0008818842859069337</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0004264106220034558</v>
+        <v>0.0008935761888598859</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0005706857753433822</v>
+        <v>0.000527098809484083</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0006144990542463208</v>
+        <v>0.0005552551541011322</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0005037535308594439</v>
+        <v>0.0007154987847545782</v>
       </c>
       <c r="G27" t="n">
-        <v>0.00026637288276816</v>
+        <v>0.0008689470933039331</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0006363807675854616</v>
+        <v>0.000891614526993382</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0005333924014792592</v>
+        <v>0.001167380686941241</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0006971632841634287</v>
+        <v>0.0006815279725632019</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0002028084059740542</v>
+        <v>0.0006347174809696875</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0005417262857800503</v>
+        <v>0.0006375080949448798</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0005184272783846249</v>
+        <v>0.0003682220361423833</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0005111994876537149</v>
+        <v>0.000665132169517861</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0004090109815816448</v>
+        <v>0.000731578850734094</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0005510897091478112</v>
+        <v>0.0008884164573648381</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.0005060271939307514</v>
+        <v>0.0008044741334036743</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0003078214618051075</v>
+        <v>0.0008620198522196764</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0004034594980463513</v>
+        <v>0.0005586628643860192</v>
       </c>
       <c r="T27" t="n">
-        <v>0.0004974326529640028</v>
+        <v>0.001454953044087533</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0006427524648391483</v>
+        <v>0.0009225983913092079</v>
       </c>
       <c r="V27" t="n">
-        <v>0.0008288522886389205</v>
+        <v>0.0009068941507796238</v>
       </c>
       <c r="W27" t="n">
-        <v>0.0003456522747666553</v>
+        <v>0.0006466014036413121</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0002166743496841912</v>
+        <v>0.0006185918119647924</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.0006629435679669607</v>
+        <v>0.0009973476617946603</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.0003131429639269767</v>
+        <v>0.001125237367763411</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.0004748862357801609</v>
+        <v>0.0006056872954320543</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.0005369691619725877</v>
+        <v>0.0008632461204295246</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.0005983992852513298</v>
+        <v>0.0005290940035375433</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.0004811106202401609</v>
+        <v>0.0006788618401932601</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0005425998295118024</v>
+        <v>0.0008875705375780867</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.000525946082381376</v>
+        <v>0.001133427177858171</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.0005488548869410098</v>
+        <v>0.0007530612045124793</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.000523541666145842</v>
+        <v>0.0004543816866252394</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.0003956653971274112</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0.0007048247341246568</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0.001235741320263744</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0.0004659127675369671</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0.0007001987251669299</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0.000405594140170559</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0.0006409105007094352</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0.0005580878048195668</v>
+        <v>0.0006276694740285502</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0004580086659977591</v>
+        <v>0.0009084662551175268</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0004968318191751726</v>
+        <v>0.000942378112062103</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0005804598443186148</v>
+        <v>0.0006643854548429914</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0004420264364507378</v>
+        <v>0.0004222623476966967</v>
       </c>
       <c r="F28" t="n">
-        <v>0.000333498746066494</v>
+        <v>0.0006050977170366761</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0004269641611632932</v>
+        <v>0.001097017867519127</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0007331224627604524</v>
+        <v>0.0007737873618162792</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0006050886785540557</v>
+        <v>0.001245984251113179</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0004070375413822185</v>
+        <v>0.0006700367527885509</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0003962404349426933</v>
+        <v>0.0003213690326329868</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0006199101740907173</v>
+        <v>0.0006970723883175175</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0003772524056897592</v>
+        <v>0.0007634568217164316</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0001941528010848316</v>
+        <v>0.0005702048693322614</v>
       </c>
       <c r="O28" t="n">
-        <v>0.000315844577539978</v>
+        <v>0.0007735772241946801</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0005129841868135675</v>
+        <v>0.0008002655683893652</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.000186931180943247</v>
+        <v>0.0006560098832237845</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0005148347503255532</v>
+        <v>0.0007865417903257894</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0004410759013792641</v>
+        <v>0.0005391786009007722</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0004293485183858439</v>
+        <v>0.001281007856925812</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0005657109787431769</v>
+        <v>0.0005711613185130872</v>
       </c>
       <c r="V28" t="n">
-        <v>0.0009730546772737447</v>
+        <v>0.0007553851604216856</v>
       </c>
       <c r="W28" t="n">
-        <v>0.0005068851263572613</v>
+        <v>0.0003079097425377763</v>
       </c>
       <c r="X28" t="n">
-        <v>0.0004189078919404024</v>
+        <v>0.0005424151211972944</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.0008463383741974387</v>
+        <v>0.0006050613532669672</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.000378483083847961</v>
+        <v>0.0009181431411320484</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.0004748862357801609</v>
+        <v>0.0006056872954320543</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.0002761184921461534</v>
+        <v>0.0006880743140473854</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.0002580914884786374</v>
+        <v>0.0006407346920301384</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.0004044719735454213</v>
+        <v>0.0005614199214680177</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0004756057647480862</v>
+        <v>0.0009947687844887013</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.0003199287311910978</v>
+        <v>0.0006780922412533263</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.0003993313597703548</v>
+        <v>0.0005666886426384275</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.000237720468419916</v>
+        <v>0.0007053676893942831</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.00031224526478686</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0.0005091084924070585</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0.001121233828405634</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0.0005031919537630629</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0.0005273879924321035</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0.0003726320954104296</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0.0005003716962965393</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.0003437056955197691</v>
+        <v>0.0005386151135327341</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0002718195129964248</v>
+        <v>0.0005227069412464189</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0005268580059777571</v>
+        <v>0.0006517486766031003</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0004153484737815141</v>
+        <v>0.0006007749978774581</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0002610036491011894</v>
+        <v>0.0006864462247417092</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0003829914220709112</v>
+        <v>0.0007873117139946992</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0004096692905454117</v>
+        <v>0.0009621210540979429</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0007379022723532234</v>
+        <v>0.0008691827846177127</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0004615411033216131</v>
+        <v>0.001203800523538596</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0004049079388057199</v>
+        <v>0.0006929442343859797</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0004361486063788166</v>
+        <v>0.0007025498464296517</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0005231396849119453</v>
+        <v>0.0008243761595616136</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0002558482951078772</v>
+        <v>0.0008585375038912454</v>
       </c>
       <c r="N29" t="n">
-        <v>0.0003182475502812896</v>
+        <v>0.0009289983221337659</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0002851706878872673</v>
+        <v>0.0009656880754145106</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0003994761968719064</v>
+        <v>0.0007189222113423455</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0003137031432597328</v>
+        <v>0.001010953855064241</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0005038601756706817</v>
+        <v>0.001162359489990121</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0003990855166946862</v>
+        <v>0.0008701370920115414</v>
       </c>
       <c r="T29" t="n">
-        <v>0.0005293857363916509</v>
+        <v>0.001207930673568518</v>
       </c>
       <c r="U29" t="n">
-        <v>0.000580727862297444</v>
+        <v>0.0009862260484851432</v>
       </c>
       <c r="V29" t="n">
-        <v>0.0009875153739988545</v>
+        <v>0.000984211648916536</v>
       </c>
       <c r="W29" t="n">
-        <v>0.0005643482003673111</v>
+        <v>0.0006218088982638105</v>
       </c>
       <c r="X29" t="n">
-        <v>0.0004893970125555967</v>
+        <v>0.0004009974240915531</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.000841221249126988</v>
+        <v>0.0008954729043457198</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.0005298194724192509</v>
+        <v>0.00120569501645554</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.0005369691619725877</v>
+        <v>0.0008632461204295246</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.0002761184921461534</v>
+        <v>0.0006880743140473854</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.0004494640403620653</v>
+        <v>0.0008744721268982257</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.0005056167390018499</v>
+        <v>0.0005873516764047807</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.0003981493076561997</v>
+        <v>0.0006494344432626295</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.0003663644505253662</v>
+        <v>0.0009468998288539283</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.000354321652449645</v>
+        <v>0.000718411595155399</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.0002661317598107058</v>
+        <v>0.0007590361364408527</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.0002500614318743203</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0.0003764972038743544</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0.001284143117127959</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.0006852271140781935</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0.0005725789809389827</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0.0005231127125014279</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.0004086423883540553</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.0003036148014970583</v>
+        <v>0.0005921991557236915</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0005706434410095498</v>
+        <v>0.001016581151108363</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0005745902505723199</v>
+        <v>0.00103306524695421</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0007487259398508012</v>
+        <v>0.0007583656241239655</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0005270550996034893</v>
+        <v>0.0005865657937358622</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0003065449352845838</v>
+        <v>0.0008466186172826985</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0005681570233592195</v>
+        <v>0.001026984392926785</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0008227020568564588</v>
+        <v>0.0009947999568604446</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0007772115090934102</v>
+        <v>0.001199325851172669</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0004806951162231559</v>
+        <v>0.0007733347257234103</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0005680953219538796</v>
+        <v>0.0005589336796566843</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0008101261009444444</v>
+        <v>0.0008756847483285075</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0004938266314896644</v>
+        <v>0.0007357340446109785</v>
       </c>
       <c r="N30" t="n">
-        <v>0.0001792498488964726</v>
+        <v>0.0006264969797449985</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0004572130831065231</v>
+        <v>0.001026713877194907</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0006027805769340739</v>
+        <v>0.0008890720220999373</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0002646670143657531</v>
+        <v>0.0009938174405712569</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0006236736829738802</v>
+        <v>0.001035777802060781</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0006544916258592041</v>
+        <v>0.0007650890176628551</v>
       </c>
       <c r="T30" t="n">
-        <v>0.0004014372396141742</v>
+        <v>0.00145803833071718</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0005998237926891607</v>
+        <v>0.0008512832125168386</v>
       </c>
       <c r="V30" t="n">
-        <v>0.001112919918296517</v>
+        <v>0.001068985995610555</v>
       </c>
       <c r="W30" t="n">
-        <v>0.0005655303400740068</v>
+        <v>0.000591062312088131</v>
       </c>
       <c r="X30" t="n">
-        <v>0.0005314107545781136</v>
+        <v>0.0007238609769096287</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.0009819442503802851</v>
+        <v>0.0009928560734641812</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.0004625834040234267</v>
+        <v>0.001241157417786165</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.0005983992852513298</v>
+        <v>0.0005290940035375433</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.0002580914884786374</v>
+        <v>0.0006407346920301384</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.0004494640403620653</v>
+        <v>0.0008744721268982257</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.0003558690235591466</v>
+        <v>0.0005781774247240949</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.0005442521538606963</v>
+        <v>0.001034515615843545</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.0003308271321726968</v>
+        <v>0.0009666022550192093</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.0005580980886915024</v>
+        <v>0.0006280357245110918</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.000330511791912184</v>
+        <v>0.000568404987194236</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.0005058894627199311</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0.0005752310661556751</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0.001024282939164273</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0.0005659342656039527</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0.0004275727011078981</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0.0004858100586737942</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0.0005518723852401552</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0.000366739981010084</v>
+        <v>0.0007162801550903946</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.00063673469988384</v>
+        <v>0.0008552209741915739</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0005817185841383895</v>
+        <v>0.0007515629875129992</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0007141320809277437</v>
+        <v>0.0006456427175463645</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0005620492960748789</v>
+        <v>0.0004956959275509188</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0003906419061804379</v>
+        <v>0.0004643627572829166</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0004762503474087923</v>
+        <v>0.0008143500127514107</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0007591934987645124</v>
+        <v>0.0005918110955092471</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0007221756201088336</v>
+        <v>0.0009535600616615847</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0005530030583348767</v>
+        <v>0.0003920860759331945</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0004897837769554735</v>
+        <v>0.0005316216467265658</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0007310420981907263</v>
+        <v>0.0006359115810677965</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0004335391011046538</v>
+        <v>0.000810283904794849</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0003363350822918965</v>
+        <v>0.0008266771603964475</v>
       </c>
       <c r="O31" t="n">
-        <v>0.000469600750816369</v>
+        <v>0.0008981584393088136</v>
       </c>
       <c r="P31" t="n">
-        <v>0.000630861376591514</v>
+        <v>0.0004248106488260604</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.00042960052547934</v>
+        <v>0.0009309378656502754</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0005267769518400164</v>
+        <v>0.0008625799906693646</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0006159250021141045</v>
+        <v>0.0006747082387983073</v>
       </c>
       <c r="T31" t="n">
-        <v>0.0003266839613341432</v>
+        <v>0.001214814162520163</v>
       </c>
       <c r="U31" t="n">
-        <v>0.0006835280912931787</v>
+        <v>0.0006573632341979451</v>
       </c>
       <c r="V31" t="n">
-        <v>0.001013149938244557</v>
+        <v>0.0007802087150548017</v>
       </c>
       <c r="W31" t="n">
-        <v>0.0004528928135599693</v>
+        <v>0.0004357866688857666</v>
       </c>
       <c r="X31" t="n">
-        <v>0.0005010804876427543</v>
+        <v>0.000372092469684801</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.0008462279346763411</v>
+        <v>0.0008428723966240696</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.0004208522212843489</v>
+        <v>0.001058817886749028</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.0004811106202401609</v>
+        <v>0.0006788618401932601</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.0004044719735454213</v>
+        <v>0.0005614199214680177</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.0005056167390018499</v>
+        <v>0.0005873516764047807</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0003558690235591466</v>
+        <v>0.0005781774247240949</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0006015527043515009</v>
+        <v>0.0008884390611920443</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.0004357727481547278</v>
+        <v>0.0008129025450509482</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.0006584344847055925</v>
+        <v>0.0003235043340283137</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.0004917410053947815</v>
+        <v>0.0007306446608610958</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.0005242800209081447</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0.0006420224366484418</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0.001146670910211079</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0.0005811182500544445</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0.0005746913675248757</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0.0005554120742671178</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.0006401386911947371</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.0004861181852683088</v>
+        <v>0.0006443614223282563</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0004839864888133459</v>
+        <v>0.0004394012415861558</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0003660048328737563</v>
+        <v>0.0007243966133843795</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0005413245969816206</v>
+        <v>0.0004793378836829273</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000276708259330582</v>
+        <v>0.000745347913321641</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0003450263562126967</v>
+        <v>0.001077862754427846</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0004548591446935832</v>
+        <v>0.0008760129335835358</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0007227529172012647</v>
+        <v>0.001129995531697361</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0005602636521006019</v>
+        <v>0.001227669806558897</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0006386900417431043</v>
+        <v>0.0009076107722873534</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0005481402809684762</v>
+        <v>0.0009597243116989928</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0007012286167475876</v>
+        <v>0.0008837769623915574</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0004156890936908</v>
+        <v>0.0008004595497682417</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0004593962650052962</v>
+        <v>0.001083177560109592</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0003449491240806433</v>
+        <v>0.0009740648987416037</v>
       </c>
       <c r="P32" t="n">
-        <v>0.0001976394164531438</v>
+        <v>0.001014559655288048</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.0004156803650866203</v>
+        <v>0.001081636348504677</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0004435478183797252</v>
+        <v>0.001254128750441704</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0006084719200472156</v>
+        <v>0.001080475589791118</v>
       </c>
       <c r="T32" t="n">
-        <v>0.0005350306033455841</v>
+        <v>0.001512803727430764</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0004507090841551163</v>
+        <v>0.001300102867372314</v>
       </c>
       <c r="V32" t="n">
-        <v>0.001157524674893792</v>
+        <v>0.001192512419575825</v>
       </c>
       <c r="W32" t="n">
-        <v>0.000482575141475442</v>
+        <v>0.000906752573306245</v>
       </c>
       <c r="X32" t="n">
-        <v>0.0004607363494101854</v>
+        <v>0.0007058422577162195</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.0009557220143431017</v>
+        <v>0.00110309392018559</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.0006004633353870325</v>
+        <v>0.001186495732728137</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.0005425998295118024</v>
+        <v>0.0008875705375780867</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.0004756057647480862</v>
+        <v>0.0009947687844887013</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.0003981493076561997</v>
+        <v>0.0006494344432626295</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.0005442521538606963</v>
+        <v>0.001034515615843545</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.0006015527043515009</v>
+        <v>0.0008884390611920443</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.000356713871584671</v>
+        <v>0.001365973226970512</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.0005114810455250569</v>
+        <v>0.001007686673724861</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.0003023373858981009</v>
+        <v>0.0006798824476457287</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.0004158316375736996</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0.0004136430826493291</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0.001303183647014702</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0.0008148522971155164</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0.0004764856478238527</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0.0006127062097622765</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0.000216345369194249</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0.0002922706686954648</v>
+        <v>0.0005725018767782988</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0005290269552407787</v>
+        <v>0.001282131115058952</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0004856311995679755</v>
+        <v>0.001314225466589096</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0006627880690012334</v>
+        <v>0.001191901080144487</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0004294285847438106</v>
+        <v>0.000879391567803137</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0003320290420748173</v>
+        <v>0.0008778135680489995</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0004629808704215372</v>
+        <v>0.001418294500181545</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0007664909792658903</v>
+        <v>0.0009089271378067144</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0006463585735761108</v>
+        <v>0.001410614924707902</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0004971789013222283</v>
+        <v>0.0009732054643194883</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0005094130073875136</v>
+        <v>0.0006298416681338918</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0006999933530774915</v>
+        <v>0.001019371376543745</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0003936183317501539</v>
+        <v>0.001317369601383706</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0002695496386098832</v>
+        <v>0.0008985019451093419</v>
       </c>
       <c r="O33" t="n">
-        <v>0.000399833866154808</v>
+        <v>0.001217969407376425</v>
       </c>
       <c r="P33" t="n">
-        <v>0.000484339174780054</v>
+        <v>0.0009430395221161433</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0003588118817553789</v>
+        <v>0.00101315323263496</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0005417707065536668</v>
+        <v>0.001041117080433517</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0005754466995528252</v>
+        <v>0.0008841895394873316</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0004796007022036646</v>
+        <v>0.001341641003077921</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0004944755697457779</v>
+        <v>0.0005442553122982906</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001080994758042145</v>
+        <v>0.0009441604981594651</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0004819684638156054</v>
+        <v>0.0006284112970857754</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0005009708213563308</v>
+        <v>0.0008930610793850243</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.00097294385714458</v>
+        <v>0.0006086969357545764</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0004680291542885329</v>
+        <v>0.001074675329436485</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.000525946082381376</v>
+        <v>0.001133427177858171</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0003199287311910978</v>
+        <v>0.0006780922412533263</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.0003663644505253662</v>
+        <v>0.0009468998288539283</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.0003308271321726968</v>
+        <v>0.0009666022550192093</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.0004357727481547278</v>
+        <v>0.0008129025450509482</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.000356713871584671</v>
+        <v>0.001365973226970512</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.0005419501462946869</v>
+        <v>0.0006592499563714405</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.0002990324904789395</v>
+        <v>0.001230261943371009</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.0004105338812994854</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0.0005454016146530969</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0.001223968522316289</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0.0006620817493031282</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0.0004160310850760175</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0.000518039577096399</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0.0004349310125794643</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0.0002643649955488178</v>
+        <v>0.0009845060932131184</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0003645856527169618</v>
+        <v>0.0009511910653918536</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0005746881975746118</v>
+        <v>0.0009475910758355988</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0004327282287032158</v>
+        <v>0.0008080353512692425</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0004543224409601875</v>
+        <v>0.0005552600653124237</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0004960767306720012</v>
+        <v>0.0005377055563496869</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0005447747687508385</v>
+        <v>0.0009741321181820562</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0007280734759209313</v>
+        <v>0.0006618781122874929</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0005649971609448657</v>
+        <v>0.001067727431068909</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0005994697547796856</v>
+        <v>0.0005973119669494136</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0004982628653137059</v>
+        <v>0.0004334546644998082</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0006261082442899926</v>
+        <v>0.0006792424553029945</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0005528949263060645</v>
+        <v>0.0009248843666296036</v>
       </c>
       <c r="N34" t="n">
-        <v>0.00045656011853653</v>
+        <v>0.0007319617459799612</v>
       </c>
       <c r="O34" t="n">
-        <v>0.0004354400254736981</v>
+        <v>0.0009831815644797842</v>
       </c>
       <c r="P34" t="n">
-        <v>0.000464913071532706</v>
+        <v>0.0005687230504021491</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0003627381835115278</v>
+        <v>0.0009474972651559398</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0005062011638943684</v>
+        <v>0.000865639127302414</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0004585945586937011</v>
+        <v>0.0006917345436792987</v>
       </c>
       <c r="T34" t="n">
-        <v>0.0005981295522392638</v>
+        <v>0.001331752685042642</v>
       </c>
       <c r="U34" t="n">
-        <v>0.0006599562516612739</v>
+        <v>0.0005783304184430297</v>
       </c>
       <c r="V34" t="n">
-        <v>0.001022155043537439</v>
+        <v>0.0007800681668697629</v>
       </c>
       <c r="W34" t="n">
-        <v>0.0006914497603056169</v>
+        <v>0.0003974665842101713</v>
       </c>
       <c r="X34" t="n">
-        <v>0.0004559603338713814</v>
+        <v>0.0005024030190695118</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.0008551905405819954</v>
+        <v>0.0007638966299073407</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.0006238812427349842</v>
+        <v>0.001019661416585284</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.0005488548869410098</v>
+        <v>0.0007530612045124793</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.0003993313597703548</v>
+        <v>0.0005666886426384275</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.000354321652449645</v>
+        <v>0.000718411595155399</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.0005580980886915024</v>
+        <v>0.0006280357245110918</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.0006584344847055925</v>
+        <v>0.0003235043340283137</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0005114810455250569</v>
+        <v>0.001007686673724861</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.0005419501462946869</v>
+        <v>0.0006592499563714405</v>
       </c>
       <c r="AH34" t="n">
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.0003464951034918227</v>
+        <v>0.000859753303003361</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.0003938074047045195</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0.0004498099094514646</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0.001222902716209092</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0.0006245503071774794</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0.0005913389563389132</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0.0005244893409741902</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.0005025774520445653</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.0004097466029764144</v>
+        <v>0.0006957836672150072</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0003699283209478568</v>
+        <v>0.0007020564609489156</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0004283309341776023</v>
+        <v>0.0008452465396217436</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0005359986213533891</v>
+        <v>0.0003892545268076657</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0002942329527747658</v>
+        <v>0.0005518713782784635</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0002445126920544164</v>
+        <v>0.0009285070802690865</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0004651184046963831</v>
+        <v>0.0009604846523259716</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0007430892353593677</v>
+        <v>0.001102605388902334</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0006007118241196243</v>
+        <v>0.001290442640298512</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0004886105137697099</v>
+        <v>0.0008053613299902657</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0004842788794533269</v>
+        <v>0.0007151249616690123</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0006895172934172761</v>
+        <v>0.0008474035363521475</v>
       </c>
       <c r="M35" t="n">
-        <v>0.000402127896269928</v>
+        <v>0.0004429517257716925</v>
       </c>
       <c r="N35" t="n">
-        <v>0.0002478179808500987</v>
+        <v>0.0007469040075734959</v>
       </c>
       <c r="O35" t="n">
-        <v>0.0002840457914687201</v>
+        <v>0.0009004918617120355</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0003331274650229183</v>
+        <v>0.001010609850550161</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0001592867591250723</v>
+        <v>0.000961619739424775</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0004780263234387109</v>
+        <v>0.001103946535114222</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0005323139220321279</v>
+        <v>0.0008789444057889219</v>
       </c>
       <c r="T35" t="n">
-        <v>0.0004423545396138253</v>
+        <v>0.001515560371552579</v>
       </c>
       <c r="U35" t="n">
-        <v>0.0004848779459640465</v>
+        <v>0.001116116977340893</v>
       </c>
       <c r="V35" t="n">
-        <v>0.001111471016422675</v>
+        <v>0.001137561387852283</v>
       </c>
       <c r="W35" t="n">
-        <v>0.0005283051255152429</v>
+        <v>0.0007302904974659164</v>
       </c>
       <c r="X35" t="n">
-        <v>0.0004138307109880311</v>
+        <v>0.0006793965809451899</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.000929926837269858</v>
+        <v>0.001066833810633681</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.0005082265179804107</v>
+        <v>0.001231952961150151</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.000523541666145842</v>
+        <v>0.0004543816866252394</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.000237720468419916</v>
+        <v>0.0007053676893942831</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.0002661317598107058</v>
+        <v>0.0007590361364408527</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.000330511791912184</v>
+        <v>0.000568404987194236</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.0004917410053947815</v>
+        <v>0.0007306446608610958</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.0003023373858981009</v>
+        <v>0.0006798824476457287</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.0002990324904789395</v>
+        <v>0.001230261943371009</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.0003464951034918227</v>
+        <v>0.000859753303003361</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.0003420038968738306</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0.000349487374416277</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0.001162268616818908</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0.0006488670911934082</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0.0004034707897814154</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0.0004804009711162637</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.0002980421530199524</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0.0001946477915186483</v>
+        <v>0.0005239486717194811</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0004821103167212461</v>
+        <v>0.0005768535541722726</v>
       </c>
       <c r="C36" t="n">
-        <v>0.000437567653459304</v>
+        <v>0.0008147277517888433</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0004307297634753671</v>
+        <v>0.0003813758961087732</v>
       </c>
       <c r="E36" t="n">
-        <v>0.000396054780798813</v>
+        <v>0.0002971606073022798</v>
       </c>
       <c r="F36" t="n">
-        <v>0.000390534465069385</v>
+        <v>0.0008440324707272598</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0002350653712598441</v>
+        <v>0.0009703002105510036</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0007436474286816025</v>
+        <v>0.0009288063845712686</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0003696782898179258</v>
+        <v>0.001205918431453031</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0004586277719223314</v>
+        <v>0.0007798494376280642</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0002627910484787949</v>
+        <v>0.0005007134953452762</v>
       </c>
       <c r="L36" t="n">
-        <v>0.000446105240706422</v>
+        <v>0.000717109612991236</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0003213001562179975</v>
+        <v>0.0006731562889613747</v>
       </c>
       <c r="N36" t="n">
-        <v>0.0003637883854206484</v>
+        <v>0.0006352440161852192</v>
       </c>
       <c r="O36" t="n">
-        <v>0.0001828279432995404</v>
+        <v>0.0007749647701224175</v>
       </c>
       <c r="P36" t="n">
-        <v>0.0004182283964566908</v>
+        <v>0.0008612354013947929</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0003681632048391821</v>
+        <v>0.0007570042972418417</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0004704460986705548</v>
+        <v>0.0009891115566372872</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0002805225905764345</v>
+        <v>0.0007629987749471919</v>
       </c>
       <c r="T36" t="n">
-        <v>0.0005883258631910845</v>
+        <v>0.001379919771193928</v>
       </c>
       <c r="U36" t="n">
-        <v>0.0005295724630322093</v>
+        <v>0.0008974312071261733</v>
       </c>
       <c r="V36" t="n">
-        <v>0.0008684720393662696</v>
+        <v>0.000927523343817744</v>
       </c>
       <c r="W36" t="n">
-        <v>0.0004769166529698889</v>
+        <v>0.0004462503027506646</v>
       </c>
       <c r="X36" t="n">
-        <v>0.0003584685698741946</v>
+        <v>0.0004996591750649421</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.0007686412718062912</v>
+        <v>0.0007474418952926169</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.0003848523607486541</v>
+        <v>0.0009395655397142416</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.0003956653971274112</v>
+        <v>0.0006276694740285502</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.00031224526478686</v>
+        <v>0.0005386151135327341</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.0002500614318743203</v>
+        <v>0.0005921991557236915</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.0005058894627199311</v>
+        <v>0.0007162801550903946</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.0005242800209081447</v>
+        <v>0.0006443614223282563</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.0004158316375736996</v>
+        <v>0.0005725018767782988</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.0004105338812994854</v>
+        <v>0.0009845060932131184</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.0003938074047045195</v>
+        <v>0.0006957836672150072</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.0003420038968738306</v>
+        <v>0.0005239486717194811</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0.0005240901847369553</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0.001269683381681549</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0.0005665448260065536</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0.000611753914814529</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0.0003543346454001478</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0.0004806180037277711</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0.0003967797442214345</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0.0002697786490594912</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.0005679874991989087</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.0004831982834021954</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.0002313421278839572</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.0004448404260821462</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.0006284985404507103</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.0008330970540029113</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.0006178366526276945</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.0005726124338257713</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.0006610073276509853</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.0007371395037430492</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.0004820084933105049</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.0004967011451134498</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0.00044019876233142</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0.0003184323151178643</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.0004226588315998742</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.0005675849860141527</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.0006561656814450122</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.0005617154385092176</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.0006131958051695242</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.001220063840911742</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.0006809842707279205</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.0005933797899873454</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0.0009853710171968443</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0.0007562359211291116</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.0007048247341246568</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0.0005091084924070585</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.0003764972038743544</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.0005752310661556751</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0.0006420224366484418</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0.0004136430826493291</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.0005454016146530969</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.0004498099094514646</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.000349487374416277</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.0005240901847369553</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0.00124919639505187</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.0008804806105605897</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0.0005602983006209197</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0.0007451188988478346</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0.0002923954646926825</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0.0003859157587918816</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0.001317741669889308</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.001174321718765846</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.001404358755389437</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.0013119968323427</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.001154056158072084</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.001297855339353161</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.001404358755389437</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.001404358755389437</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.001152231293809118</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.001238068881017549</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.001404358755389437</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0.001325024860954808</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0.001117573015456794</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.001215611854148644</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0.001291860368962209</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0.00111272331370253</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0.001299925148651584</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0.001298031303712368</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0.001141188416098326</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0.001147212557189824</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0.001404358755389437</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.00121476054647129</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0.001158893716539277</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0.001404358755389437</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0.001139788038290065</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.001235741320263744</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.001121233828405634</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.001284143117127959</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.001024282939164273</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0.001146670910211079</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.001303183647014702</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.001223968522316289</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.001222902716209092</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.001162268616818908</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.001269683381681549</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0.00124919639505187</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0.0009832776001510643</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0.001124601520246129</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0.001096827156456526</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.001247959762995501</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.001242205458213547</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0.0008459267421384435</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.0006634900459314878</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.0008130752717807557</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.0008409718419795574</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.0006501954951292626</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.0005709460674588921</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.0008795857330529143</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.000763403346168117</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.0006772959867778977</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.0004466690121740929</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.0007187159464830739</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.0007418677599864022</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.0005415157124515794</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.0006074597395443141</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.0008249673673920596</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.0005821655307279151</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0.0006837405462107979</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.0005416764193828122</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0.0006729581843660156</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.0007553069501518017</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.0007986312118106517</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0.0006364220672604184</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0.0004783161688815617</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0.0008225917198983994</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0.000386923745288981</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.0004659127675369671</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0.0005031919537630629</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0.0006852271140781935</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.0005659342656039527</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0.0005811182500544445</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0.0008148522971155164</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0.0006620817493031282</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0.0006245503071774794</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0.0006488670911934082</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.0005665448260065536</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0.0008804806105605897</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0.0009832776001510643</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0.0007520113929136926</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0.0003319470844324377</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0.0008530000106906529</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.0007190326003145476</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0.0006169735732953483</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.0006182091938677395</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.0007916012243755582</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.0005349396953257963</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.0003693232329259661</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.0006764319263355303</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.000910090999087875</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.0008403883344662393</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.0006800256828841852</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.0007221846935032954</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.0009480465755461292</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.0006624929569060341</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.0003963930482713133</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0.0005573943162675215</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0.000541561460560792</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0.0004436200722629566</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.0006781976894288574</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0.000810283016877101</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0.0005811778551751559</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0.0005995069945716947</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0.001284143117127959</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.000692446519567742</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0.0006194939211948156</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0.001133216460475571</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0.0006749650440321886</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.0007001987251669299</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0.0005273879924321035</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0.0005725789809389827</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.0004275727011078981</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0.0005746913675248757</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.0004764856478238527</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.0004160310850760175</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0.0005913389563389132</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0.0004034707897814154</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.000611753914814529</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0.0005602983006209197</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0.001124601520246129</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0.0007520113929136926</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0.0006375436690249012</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0.0004699910111645215</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0.0003318953599041475</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0.0007222553245433978</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.0005231151869138896</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.0006825030912465269</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.0006629158738114783</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.0004733742100680559</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.0003875668463317446</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.000801953258265424</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.0006277154221690968</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.0005759330160877631</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.0003396182315554075</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.0006477403157050472</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.0005745963134237983</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0.00042235654907804</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0.0003995981077105706</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0.0006448963669467978</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.0004314107759993923</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.0005886075958012556</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0.0004594149476663624</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0.0006298223230030076</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0.0006213649674098064</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0.0008333907299767398</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0.0005252177954979158</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0.0003788509272640141</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0.0007917473588530395</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0.0002496947908462402</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0.000405594140170559</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0.0003726320954104296</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0.0005231127125014279</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0.0004858100586737942</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0.0005554120742671178</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0.0006127062097622765</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0.000518039577096399</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0.0005244893409741902</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0.0004804009711162637</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0.0003543346454001478</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0.0007451188988478346</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0.001096827156456526</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0.0003319470844324377</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>0.0006375436690249012</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0.0006847767741504327</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0.0005534653688880799</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0.0004386169712677647</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.0003969471304691086</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.000579883434644972</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.0002483517573271248</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.0003857092896448988</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.0005656445559578215</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.0008507506586479025</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.0006076333756878668</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.0005997585203658582</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.0006232545144549837</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.0007510019441552301</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.0004740218697547196</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.0004740586013895055</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0.0003838916299711895</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.0001814147696005705</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.0004325807878923427</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.0005409337387696236</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.0006528432216315915</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0.0005730557844268713</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.0004160883888710267</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.001233067413130983</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0.0005669017506568095</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0.0005210329363511057</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0.001049142094754232</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0.000693666510439437</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.0006409105007094352</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0.0005003716962965393</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0.0004086423883540553</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.0005518723852401552</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0.0006401386911947371</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.000216345369194249</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.0004349310125794643</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0.0005025774520445653</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0.0002980421530199524</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.0004806180037277711</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0.0002923954646926825</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0.001247959762995501</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0.0008530000106906529</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>0.0004699910111645215</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0.0006847767741504327</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0.0003385913154085668</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>United States of America</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0.0003704476928184742</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.0005179754234304361</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.0005488723217234611</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.0002891177906162364</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.0002320044116464537</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.0004814930842745714</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.0007180848576452959</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.0006342264418206498</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.0005585010269372639</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.0005425832471364714</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.0007358411122708047</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.0004109063483280628</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.0002681119536849518</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0.0003628859048749979</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0.0003645015399805935</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0.0002595290245289932</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.0004861026534371755</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0.0006028779114326427</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0.0004534808355022137</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0.0005624374865160486</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0.001144008534161368</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0.0005706793862412822</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.0004871130194666149</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0.0009447162758951851</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0.0005551214085929344</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.0005580878048195668</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0.0003437056955197691</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0.0003036148014970583</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0.000366739981010084</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0.0004861181852683088</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.0002922706686954648</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.0002643649955488178</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0.0004097466029764144</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0.0001946477915186483</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.0003967797442214345</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0.0003859157587918816</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0.001242205458213547</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0.0007190326003145476</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>0.0003318953599041475</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0.0005534653688880799</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0.0003385913154085668</v>
-      </c>
-      <c r="AQ43" t="n">
         <v>0</v>
       </c>
     </row>
